--- a/survey_templates/036_child_screen_time_survey--survey_templates.xlsx
+++ b/survey_templates/036_child_screen_time_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -889,8 +889,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -918,12 +918,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'under_2_years',_'value':_'baby'}</t>
+          <t>under_2_years</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Under 2 years', 'value': 'baby'}</t>
+          <t>Under 2 years</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'2_to_5_years',_'value':_'toddler'}</t>
+          <t>2_to_5_years</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': '2 to 5 years', 'value': 'toddler'}</t>
+          <t>2 to 5 years</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'6_to_10_years',_'value':_'child'}</t>
+          <t>6_to_10_years</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': '6 to 10 years', 'value': 'child'}</t>
+          <t>6 to 10 years</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'11_to_13_years',_'value':_'tween'}</t>
+          <t>11_to_13_years</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': '11 to 13 years', 'value': 'tween'}</t>
+          <t>11 to 13 years</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'14_to_17_years',_'value':_'teen'}</t>
+          <t>14_to_17_years</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': '14 to 17 years', 'value': 'teen'}</t>
+          <t>14 to 17 years</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'smartphone',_'value':_'phone'}</t>
+          <t>smartphone</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Smartphone', 'value': 'phone'}</t>
+          <t>Smartphone</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'tablet_or_ipad',_'value':_'tablet'}</t>
+          <t>tablet_or_ipad</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Tablet or IPad', 'value': 'tablet'}</t>
+          <t>Tablet or IPad</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'television',_'value':_'tv'}</t>
+          <t>television</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Television', 'value': 'tv'}</t>
+          <t>Television</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'computer_or_laptop',_'value':_'computer'}</t>
+          <t>computer_or_laptop</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Computer or Laptop', 'value': 'computer'}</t>
+          <t>Computer or Laptop</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'gaming_console',_'value':_'console'}</t>
+          <t>gaming_console</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Gaming Console', 'value': 'console'}</t>
+          <t>Gaming Console</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'educational_games_and_apps',_'value':_'educational'}</t>
+          <t>educational_games_and_apps</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Educational games and apps', 'value': 'educational'}</t>
+          <t>Educational games and apps</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'videos_or_youtube',_'value':_'videos'}</t>
+          <t>videos_or_youtube</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Videos or YouTube', 'value': 'videos'}</t>
+          <t>Videos or YouTube</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'social_media_or_messaging',_'value':_'social'}</t>
+          <t>social_media_or_messaging</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Social media or Messaging', 'value': 'social'}</t>
+          <t>Social media or Messaging</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'entertainment_video_games',_'value':_'gaming'}</t>
+          <t>entertainment_video_games</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Entertainment Video games', 'value': 'gaming'}</t>
+          <t>Entertainment Video games</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'school_work_and_research',_'value':_'school'}</t>
+          <t>school_work_and_research</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'School work and Research', 'value': 'school'}</t>
+          <t>School work and Research</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'yes_-_always_active',_'value':_'always'}</t>
+          <t>yes_-_always_active</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Yes - Always Active', 'value': 'always'}</t>
+          <t>Yes - Always Active</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'yes_-_sometimes_active',_'value':_'sometimes'}</t>
+          <t>yes_-_sometimes_active</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Yes - Sometimes Active', 'value': 'sometimes'}</t>
+          <t>Yes - Sometimes Active</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'no_-_not_used',_'value':_false}</t>
+          <t>no_-_not_used</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'No - Not used', 'value': False}</t>
+          <t>No - Not used</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'positively_-_helps_learning',_'value':_'positive'}</t>
+          <t>positively_-_helps_learning</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Positively - Helps learning', 'value': 'positive'}</t>
+          <t>Positively - Helps learning</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'neutrally_-_no_major_change',_'value':_'neutral'}</t>
+          <t>neutrally_-_no_major_change</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Neutrally - No major change', 'value': 'neutral'}</t>
+          <t>Neutrally - No major change</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'negatively_-_causes_irritability',_'value':_'negative'}</t>
+          <t>negatively_-_causes_irritability</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Negatively - Causes irritability', 'value': 'negative'}</t>
+          <t>Negatively - Causes irritability</t>
         </is>
       </c>
     </row>
